--- a/artfynd/A 31655-2026 artfynd.xlsx
+++ b/artfynd/A 31655-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193921</v>
       </c>
       <c r="B2" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31655-2026 artfynd.xlsx
+++ b/artfynd/A 31655-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193921</v>
       </c>
       <c r="B2" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31655-2026 artfynd.xlsx
+++ b/artfynd/A 31655-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193921</v>
       </c>
       <c r="B2" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136193876</v>
       </c>
       <c r="B3" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31655-2026 artfynd.xlsx
+++ b/artfynd/A 31655-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193921</v>
       </c>
       <c r="B2" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
